--- a/public/assets/excel_formats/activityFormat.xlsx
+++ b/public/assets/excel_formats/activityFormat.xlsx
@@ -1,32 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SGAMarketAudit\public\assets\excel_formats\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\marketaudit_tnbttech\public\assets\excel_formats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0029746E-DE82-4F06-9BEC-5E62FC9701B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D112FD28-09B4-4644-BAD9-E6BCE1EF896B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>Sr.Number</t>
   </si>
@@ -37,6 +32,21 @@
     <t>Question Type</t>
   </si>
   <si>
+    <t>Answer Type</t>
+  </si>
+  <si>
+    <t>Is Child</t>
+  </si>
+  <si>
+    <t>Sub Question Of (Seq No.)</t>
+  </si>
+  <si>
+    <t>Sub Question Sequence</t>
+  </si>
+  <si>
+    <t>Multiple Answers Allowed</t>
+  </si>
+  <si>
     <t>Yes / No</t>
   </si>
   <si>
@@ -49,6 +59,9 @@
     <t>Dropdown</t>
   </si>
   <si>
+    <t>Multi select</t>
+  </si>
+  <si>
     <t>Image</t>
   </si>
   <si>
@@ -58,35 +71,36 @@
     <t>Date</t>
   </si>
   <si>
+    <t>Date &amp; Time</t>
+  </si>
+  <si>
     <t>File Upload</t>
   </si>
   <si>
     <t>Location</t>
   </si>
   <si>
-    <t>Date &amp; Time</t>
-  </si>
-  <si>
-    <t>Answer Type</t>
-  </si>
-  <si>
-    <t>Multi select</t>
-  </si>
-  <si>
     <t>Audio</t>
+  </si>
+  <si>
+    <t>Multi Response</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -97,7 +111,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -107,32 +121,45 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -187,7 +214,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -239,7 +266,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -300,157 +327,184 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D21"/>
-  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:H21"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.08203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.08203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="13" customWidth="1"/>
+    <col min="3" max="3" width="17" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="29" customWidth="1"/>
+    <col min="7" max="7" width="25" customWidth="1"/>
+    <col min="8" max="8" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -461,214 +515,245 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E2" s="1"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E3" s="1"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E4" s="1"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E5" s="1"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E6" s="1"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E7" s="1"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E8" s="1"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E9" s="1"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E10" s="1"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E11" s="1"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E12" s="1"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E13" s="1"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E14" s="1"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E15" s="1"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E16" s="1"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E17" s="1"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E18" s="1"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E19" s="1"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E20" s="1"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D21" xr:uid="{38272F7E-4801-499D-A902-27491C30AAD1}">
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D21" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Required, Optional"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E21" xr:uid="{00000000-0002-0000-0000-000001000000}">
+      <formula1>"Yes"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid" error="Please select Yes or No." promptTitle="Multiple Answers Allowed" prompt="Yes = auditor can upload multiple images (Image type only)." sqref="H2:H100" xr:uid="{00000000-0002-0000-0000-000002000000}">
+      <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
-          <x14:formula1>
-            <xm:f>Sheet2!$A$1:$A$12</xm:f>
-          </x14:formula1>
-          <xm:sqref>C1:C1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:A12"/>
-  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:A13"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/public/assets/excel_formats/activityFormat.xlsx
+++ b/public/assets/excel_formats/activityFormat.xlsx
@@ -1,27 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\marketaudit_tnbttech\public\assets\excel_formats\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6956394A-3E3A-4AE6-BE07-35C516BB52AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet name="Questions" sheetId="1" r:id="rId1"/>
-    <sheet name="Instructions" sheetId="2" r:id="rId2"/>
+    <sheet name="Questions" sheetId="1" r:id="rId4"/>
+    <sheet name="Instructions" sheetId="2" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="56">
   <si>
     <t>Sr. Number</t>
   </si>
@@ -95,7 +90,7 @@
     <t>Hint / instruction text shown below the question (optional)</t>
   </si>
   <si>
-    <t>Dropdown / Multi select: pipe-separated choices  e.g.  Option A|Option B|Option C</t>
+    <t>Dropdown / Multi select: pipe-separated choices e.g. Option A|Option B|Option C.  Barcode / QR Code / RFID: pipe-separated expected headers e.g. cooler_id|serial_number (optional)</t>
   </si>
   <si>
     <t>Multi select only — Yes = auditor can choose multiple options; No or blank = single choice</t>
@@ -134,63 +129,6 @@
     <t>Conditional: paste exact question_text of the PARENT question.
 Works with YES/NO, Dropdown, Free Text, Date, Image, and ALL types.
 Leave blank if this is NOT a conditional question.</t>
-  </si>
-  <si>
-    <t>Column</t>
-  </si>
-  <si>
-    <t>Description / Valid Values</t>
-  </si>
-  <si>
-    <t>1, 2, 3 ... (sequential)</t>
-  </si>
-  <si>
-    <t>Yes / No | Free Text | Subjective | Dropdown | Multi select | Image | Video | Date | Date &amp; Time | File Upload | Location | Audio | Multi Response  REQUIRED</t>
-  </si>
-  <si>
-    <t>Required   or   Optional  REQUIRED</t>
-  </si>
-  <si>
-    <t>Optional hint text shown below the question on the form</t>
-  </si>
-  <si>
-    <t>Pipe-separated choices for Dropdown / Multi select  e.g.  Option A|Option B|Option C</t>
-  </si>
-  <si>
-    <t>[Multi select ONLY] Yes = auditor can pick multiple options; No or blank = single selection</t>
-  </si>
-  <si>
-    <t>[Image ONLY] Yes = auditor can upload multiple images (+ button); No or blank = single image upload</t>
-  </si>
-  <si>
-    <t>none | numericrange | digitlength | textlength | email | phone | regex</t>
-  </si>
-  <si>
-    <t>numericrange: min number | digitlength: min digits | textlength: min chars</t>
-  </si>
-  <si>
-    <t>numericrange: max number | digitlength: max digits | textlength: max chars</t>
-  </si>
-  <si>
-    <t>Custom regex — only when validation_rule = regex</t>
-  </si>
-  <si>
-    <t>Comma-separated extensions for Image / File Upload  e.g.  .jpg,.png,.pdf</t>
-  </si>
-  <si>
-    <t>Max file size in MB for Image / File Upload  e.g.  10</t>
-  </si>
-  <si>
-    <t>Earliest allowed date for Date / Date &amp; Time  YYYY-MM-DD</t>
-  </si>
-  <si>
-    <t>Latest allowed date for Date / Date &amp; Time  YYYY-MM-DD</t>
-  </si>
-  <si>
-    <t>Conditional: paste exact question_text of the parent Yes/No or Dropdown question</t>
-  </si>
-  <si>
-    <t>Conditional: parent answer that reveals this question  e.g.  Yes  or  Option A</t>
   </si>
   <si>
     <t>Conditional trigger value:
@@ -200,48 +138,127 @@
   -&gt; Shows whenever parent has ANY answer (non-empty)
   Works for: Free Text, Date, Image, Location, etc.</t>
   </si>
+  <si>
+    <t>Column</t>
+  </si>
+  <si>
+    <t>Description / Valid Values</t>
+  </si>
+  <si>
+    <t>1, 2, 3 ... (sequential)</t>
+  </si>
+  <si>
+    <t>Yes / No | Free Text | Subjective | Dropdown | Multi select | Image | Video | Date | Date &amp; Time | File Upload | Location | Audio | Multi Response  REQUIRED</t>
+  </si>
+  <si>
+    <t>Required   or   Optional  REQUIRED</t>
+  </si>
+  <si>
+    <t>Optional hint text shown below the question on the form</t>
+  </si>
+  <si>
+    <t>[Multi select ONLY] Yes = auditor can pick multiple options; No or blank = single selection</t>
+  </si>
+  <si>
+    <t>[Image ONLY] Yes = auditor can upload multiple images (+ button); No or blank = single image upload</t>
+  </si>
+  <si>
+    <t>none | numericrange | digitlength | textlength | email | phone | regex</t>
+  </si>
+  <si>
+    <t>numericrange: min number | digitlength: min digits | textlength: min chars</t>
+  </si>
+  <si>
+    <t>numericrange: max number | digitlength: max digits | textlength: max chars</t>
+  </si>
+  <si>
+    <t>Custom regex — only when validation_rule = regex</t>
+  </si>
+  <si>
+    <t>Comma-separated extensions for Image / File Upload  e.g.  .jpg,.png,.pdf</t>
+  </si>
+  <si>
+    <t>Max file size in MB for Image / File Upload  e.g.  10</t>
+  </si>
+  <si>
+    <t>Earliest allowed date for Date / Date &amp; Time  YYYY-MM-DD</t>
+  </si>
+  <si>
+    <t>Latest allowed date for Date / Date &amp; Time  YYYY-MM-DD</t>
+  </si>
+  <si>
+    <t>Conditional: paste exact question_text of the parent Yes/No or Dropdown question</t>
+  </si>
+  <si>
+    <t>Conditional: parent answer that reveals this question  e.g.  Yes  or  Option A</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
+  <numFmts count="0"/>
+  <fonts count="7">
     <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <i/>
+      <b val="0"/>
+      <i val="1"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="9"/>
       <color rgb="FF8B0000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <i/>
+      <b val="0"/>
+      <i val="1"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="9"/>
       <color rgb="FF595959"/>
       <name val="Calibri"/>
     </font>
     <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="10"/>
       <color rgb="FF1F1F1F"/>
       <name val="Calibri"/>
@@ -257,41 +274,49 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F3864"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF375623"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F538C"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9E1F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF375623"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F538C"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF5F5F5"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEBF3FB"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
@@ -323,54 +348,46 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="12">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="3" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="4" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="5" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="6" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="7" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="8" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf xfId="0" fontId="5" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf xfId="0" fontId="6" numFmtId="0" fillId="9" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf xfId="0" fontId="6" numFmtId="0" fillId="7" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="6" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
 </styleSheet>
 </file>
 
@@ -658,27 +675,35 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
   <dimension ref="A1:S100"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="42" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="34" customWidth="1"/>
-    <col min="6" max="6" width="44" customWidth="1"/>
-    <col min="7" max="8" width="26" customWidth="1"/>
-    <col min="9" max="9" width="22" customWidth="1"/>
-    <col min="10" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="30" customWidth="1"/>
-    <col min="13" max="13" width="28" customWidth="1"/>
-    <col min="14" max="16" width="22" customWidth="1"/>
-    <col min="17" max="18" width="42" customWidth="1"/>
-    <col min="19" max="19" width="36" customWidth="1"/>
+    <col min="1" max="1" width="12" customWidth="true" style="0"/>
+    <col min="2" max="2" width="42" customWidth="true" style="0"/>
+    <col min="3" max="3" width="24" customWidth="true" style="0"/>
+    <col min="4" max="4" width="16" customWidth="true" style="0"/>
+    <col min="5" max="5" width="34" customWidth="true" style="0"/>
+    <col min="6" max="6" width="44" customWidth="true" style="0"/>
+    <col min="7" max="7" width="26" customWidth="true" style="0"/>
+    <col min="8" max="8" width="26" customWidth="true" style="0"/>
+    <col min="9" max="9" width="22" customWidth="true" style="0"/>
+    <col min="10" max="10" width="18" customWidth="true" style="0"/>
+    <col min="11" max="11" width="18" customWidth="true" style="0"/>
+    <col min="12" max="12" width="30" customWidth="true" style="0"/>
+    <col min="13" max="13" width="28" customWidth="true" style="0"/>
+    <col min="14" max="14" width="22" customWidth="true" style="0"/>
+    <col min="15" max="15" width="22" customWidth="true" style="0"/>
+    <col min="16" max="16" width="22" customWidth="true" style="0"/>
+    <col min="17" max="17" width="42" customWidth="true" style="0"/>
+    <col min="18" max="18" width="42" customWidth="true" style="0"/>
+    <col min="19" max="19" width="36" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" customHeight="1" ht="34.05">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -737,7 +762,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" customHeight="1" ht="60">
       <c r="A2" s="4" t="s">
         <v>19</v>
       </c>
@@ -793,10 +818,10 @@
         <v>36</v>
       </c>
       <c r="S2" s="11" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" customHeight="1" ht="18">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -817,7 +842,7 @@
       <c r="R3" s="6"/>
       <c r="S3" s="6"/>
     </row>
-    <row r="4" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" customHeight="1" ht="18">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -838,7 +863,7 @@
       <c r="R4" s="7"/>
       <c r="S4" s="7"/>
     </row>
-    <row r="5" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" customHeight="1" ht="18">
       <c r="A5" s="6"/>
       <c r="B5" s="6"/>
       <c r="C5" s="6"/>
@@ -859,7 +884,7 @@
       <c r="R5" s="6"/>
       <c r="S5" s="6"/>
     </row>
-    <row r="6" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" customHeight="1" ht="18">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
@@ -880,7 +905,7 @@
       <c r="R6" s="7"/>
       <c r="S6" s="7"/>
     </row>
-    <row r="7" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" customHeight="1" ht="18">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -901,7 +926,7 @@
       <c r="R7" s="6"/>
       <c r="S7" s="6"/>
     </row>
-    <row r="8" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" customHeight="1" ht="18">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
@@ -922,7 +947,7 @@
       <c r="R8" s="7"/>
       <c r="S8" s="7"/>
     </row>
-    <row r="9" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" customHeight="1" ht="18">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -943,7 +968,7 @@
       <c r="R9" s="6"/>
       <c r="S9" s="6"/>
     </row>
-    <row r="10" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" customHeight="1" ht="18">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
@@ -964,7 +989,7 @@
       <c r="R10" s="7"/>
       <c r="S10" s="7"/>
     </row>
-    <row r="11" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" customHeight="1" ht="18">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -985,7 +1010,7 @@
       <c r="R11" s="6"/>
       <c r="S11" s="6"/>
     </row>
-    <row r="12" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" customHeight="1" ht="18">
       <c r="A12" s="7"/>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
@@ -1006,7 +1031,7 @@
       <c r="R12" s="7"/>
       <c r="S12" s="7"/>
     </row>
-    <row r="13" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" customHeight="1" ht="18">
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
@@ -1027,7 +1052,7 @@
       <c r="R13" s="6"/>
       <c r="S13" s="6"/>
     </row>
-    <row r="14" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" customHeight="1" ht="18">
       <c r="A14" s="7"/>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
@@ -1048,7 +1073,7 @@
       <c r="R14" s="7"/>
       <c r="S14" s="7"/>
     </row>
-    <row r="15" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" customHeight="1" ht="18">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
@@ -1069,7 +1094,7 @@
       <c r="R15" s="6"/>
       <c r="S15" s="6"/>
     </row>
-    <row r="16" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:19" customHeight="1" ht="18">
       <c r="A16" s="7"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
@@ -1090,7 +1115,7 @@
       <c r="R16" s="7"/>
       <c r="S16" s="7"/>
     </row>
-    <row r="17" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:19" customHeight="1" ht="18">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -1111,7 +1136,7 @@
       <c r="R17" s="6"/>
       <c r="S17" s="6"/>
     </row>
-    <row r="18" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:19" customHeight="1" ht="18">
       <c r="A18" s="7"/>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -1132,7 +1157,7 @@
       <c r="R18" s="7"/>
       <c r="S18" s="7"/>
     </row>
-    <row r="19" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:19" customHeight="1" ht="18">
       <c r="A19" s="6"/>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
@@ -1153,7 +1178,7 @@
       <c r="R19" s="6"/>
       <c r="S19" s="6"/>
     </row>
-    <row r="20" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:19" customHeight="1" ht="18">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -1174,7 +1199,7 @@
       <c r="R20" s="7"/>
       <c r="S20" s="7"/>
     </row>
-    <row r="21" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:19" customHeight="1" ht="18">
       <c r="A21" s="6"/>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -1195,7 +1220,7 @@
       <c r="R21" s="6"/>
       <c r="S21" s="6"/>
     </row>
-    <row r="22" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:19" customHeight="1" ht="18">
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
@@ -1216,7 +1241,7 @@
       <c r="R22" s="7"/>
       <c r="S22" s="7"/>
     </row>
-    <row r="23" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:19" customHeight="1" ht="18">
       <c r="A23" s="6"/>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
@@ -1237,7 +1262,7 @@
       <c r="R23" s="6"/>
       <c r="S23" s="6"/>
     </row>
-    <row r="24" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:19" customHeight="1" ht="18">
       <c r="A24" s="7"/>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
@@ -1258,7 +1283,7 @@
       <c r="R24" s="7"/>
       <c r="S24" s="7"/>
     </row>
-    <row r="25" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:19" customHeight="1" ht="18">
       <c r="A25" s="6"/>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
@@ -1279,7 +1304,7 @@
       <c r="R25" s="6"/>
       <c r="S25" s="6"/>
     </row>
-    <row r="26" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:19" customHeight="1" ht="18">
       <c r="A26" s="7"/>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
@@ -1300,7 +1325,7 @@
       <c r="R26" s="7"/>
       <c r="S26" s="7"/>
     </row>
-    <row r="27" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:19" customHeight="1" ht="18">
       <c r="A27" s="6"/>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
@@ -1321,7 +1346,7 @@
       <c r="R27" s="6"/>
       <c r="S27" s="6"/>
     </row>
-    <row r="28" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:19" customHeight="1" ht="18">
       <c r="A28" s="7"/>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
@@ -1342,7 +1367,7 @@
       <c r="R28" s="7"/>
       <c r="S28" s="7"/>
     </row>
-    <row r="29" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:19" customHeight="1" ht="18">
       <c r="A29" s="6"/>
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
@@ -1363,7 +1388,7 @@
       <c r="R29" s="6"/>
       <c r="S29" s="6"/>
     </row>
-    <row r="30" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:19" customHeight="1" ht="18">
       <c r="A30" s="7"/>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
@@ -1384,7 +1409,7 @@
       <c r="R30" s="7"/>
       <c r="S30" s="7"/>
     </row>
-    <row r="31" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:19" customHeight="1" ht="18">
       <c r="A31" s="6"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
@@ -1405,7 +1430,7 @@
       <c r="R31" s="6"/>
       <c r="S31" s="6"/>
     </row>
-    <row r="32" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:19" customHeight="1" ht="18">
       <c r="A32" s="7"/>
       <c r="B32" s="7"/>
       <c r="C32" s="7"/>
@@ -1426,7 +1451,7 @@
       <c r="R32" s="7"/>
       <c r="S32" s="7"/>
     </row>
-    <row r="33" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:19" customHeight="1" ht="18">
       <c r="A33" s="6"/>
       <c r="B33" s="6"/>
       <c r="C33" s="6"/>
@@ -1447,7 +1472,7 @@
       <c r="R33" s="6"/>
       <c r="S33" s="6"/>
     </row>
-    <row r="34" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:19" customHeight="1" ht="18">
       <c r="A34" s="7"/>
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
@@ -1468,7 +1493,7 @@
       <c r="R34" s="7"/>
       <c r="S34" s="7"/>
     </row>
-    <row r="35" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:19" customHeight="1" ht="18">
       <c r="A35" s="6"/>
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
@@ -1489,7 +1514,7 @@
       <c r="R35" s="6"/>
       <c r="S35" s="6"/>
     </row>
-    <row r="36" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:19" customHeight="1" ht="18">
       <c r="A36" s="7"/>
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
@@ -1510,7 +1535,7 @@
       <c r="R36" s="7"/>
       <c r="S36" s="7"/>
     </row>
-    <row r="37" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:19" customHeight="1" ht="18">
       <c r="A37" s="6"/>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
@@ -1531,7 +1556,7 @@
       <c r="R37" s="6"/>
       <c r="S37" s="6"/>
     </row>
-    <row r="38" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:19" customHeight="1" ht="18">
       <c r="A38" s="7"/>
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
@@ -1552,7 +1577,7 @@
       <c r="R38" s="7"/>
       <c r="S38" s="7"/>
     </row>
-    <row r="39" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:19" customHeight="1" ht="18">
       <c r="A39" s="6"/>
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>
@@ -1573,7 +1598,7 @@
       <c r="R39" s="6"/>
       <c r="S39" s="6"/>
     </row>
-    <row r="40" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:19" customHeight="1" ht="18">
       <c r="A40" s="7"/>
       <c r="B40" s="7"/>
       <c r="C40" s="7"/>
@@ -1594,7 +1619,7 @@
       <c r="R40" s="7"/>
       <c r="S40" s="7"/>
     </row>
-    <row r="41" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:19" customHeight="1" ht="18">
       <c r="A41" s="6"/>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -1615,7 +1640,7 @@
       <c r="R41" s="6"/>
       <c r="S41" s="6"/>
     </row>
-    <row r="42" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:19" customHeight="1" ht="18">
       <c r="A42" s="7"/>
       <c r="B42" s="7"/>
       <c r="C42" s="7"/>
@@ -1636,7 +1661,7 @@
       <c r="R42" s="7"/>
       <c r="S42" s="7"/>
     </row>
-    <row r="43" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:19" customHeight="1" ht="18">
       <c r="A43" s="6"/>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
@@ -1657,7 +1682,7 @@
       <c r="R43" s="6"/>
       <c r="S43" s="6"/>
     </row>
-    <row r="44" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:19" customHeight="1" ht="18">
       <c r="A44" s="7"/>
       <c r="B44" s="7"/>
       <c r="C44" s="7"/>
@@ -1678,7 +1703,7 @@
       <c r="R44" s="7"/>
       <c r="S44" s="7"/>
     </row>
-    <row r="45" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:19" customHeight="1" ht="18">
       <c r="A45" s="6"/>
       <c r="B45" s="6"/>
       <c r="C45" s="6"/>
@@ -1699,7 +1724,7 @@
       <c r="R45" s="6"/>
       <c r="S45" s="6"/>
     </row>
-    <row r="46" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:19" customHeight="1" ht="18">
       <c r="A46" s="7"/>
       <c r="B46" s="7"/>
       <c r="C46" s="7"/>
@@ -1720,7 +1745,7 @@
       <c r="R46" s="7"/>
       <c r="S46" s="7"/>
     </row>
-    <row r="47" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:19" customHeight="1" ht="18">
       <c r="A47" s="6"/>
       <c r="B47" s="6"/>
       <c r="C47" s="6"/>
@@ -1741,7 +1766,7 @@
       <c r="R47" s="6"/>
       <c r="S47" s="6"/>
     </row>
-    <row r="48" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:19" customHeight="1" ht="18">
       <c r="A48" s="7"/>
       <c r="B48" s="7"/>
       <c r="C48" s="7"/>
@@ -1762,7 +1787,7 @@
       <c r="R48" s="7"/>
       <c r="S48" s="7"/>
     </row>
-    <row r="49" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:19" customHeight="1" ht="18">
       <c r="A49" s="6"/>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
@@ -1783,7 +1808,7 @@
       <c r="R49" s="6"/>
       <c r="S49" s="6"/>
     </row>
-    <row r="50" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:19" customHeight="1" ht="18">
       <c r="A50" s="7"/>
       <c r="B50" s="7"/>
       <c r="C50" s="7"/>
@@ -1804,7 +1829,7 @@
       <c r="R50" s="7"/>
       <c r="S50" s="7"/>
     </row>
-    <row r="51" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:19" customHeight="1" ht="18">
       <c r="A51" s="6"/>
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
@@ -1825,7 +1850,7 @@
       <c r="R51" s="6"/>
       <c r="S51" s="6"/>
     </row>
-    <row r="52" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:19" customHeight="1" ht="18">
       <c r="A52" s="7"/>
       <c r="B52" s="7"/>
       <c r="C52" s="7"/>
@@ -1846,7 +1871,7 @@
       <c r="R52" s="7"/>
       <c r="S52" s="7"/>
     </row>
-    <row r="53" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:19" customHeight="1" ht="18">
       <c r="A53" s="6"/>
       <c r="B53" s="6"/>
       <c r="C53" s="6"/>
@@ -1867,7 +1892,7 @@
       <c r="R53" s="6"/>
       <c r="S53" s="6"/>
     </row>
-    <row r="54" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:19" customHeight="1" ht="18">
       <c r="A54" s="7"/>
       <c r="B54" s="7"/>
       <c r="C54" s="7"/>
@@ -1888,7 +1913,7 @@
       <c r="R54" s="7"/>
       <c r="S54" s="7"/>
     </row>
-    <row r="55" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:19" customHeight="1" ht="18">
       <c r="A55" s="6"/>
       <c r="B55" s="6"/>
       <c r="C55" s="6"/>
@@ -1909,7 +1934,7 @@
       <c r="R55" s="6"/>
       <c r="S55" s="6"/>
     </row>
-    <row r="56" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:19" customHeight="1" ht="18">
       <c r="A56" s="7"/>
       <c r="B56" s="7"/>
       <c r="C56" s="7"/>
@@ -1930,7 +1955,7 @@
       <c r="R56" s="7"/>
       <c r="S56" s="7"/>
     </row>
-    <row r="57" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:19" customHeight="1" ht="18">
       <c r="A57" s="6"/>
       <c r="B57" s="6"/>
       <c r="C57" s="6"/>
@@ -1951,7 +1976,7 @@
       <c r="R57" s="6"/>
       <c r="S57" s="6"/>
     </row>
-    <row r="58" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:19" customHeight="1" ht="18">
       <c r="A58" s="7"/>
       <c r="B58" s="7"/>
       <c r="C58" s="7"/>
@@ -1972,7 +1997,7 @@
       <c r="R58" s="7"/>
       <c r="S58" s="7"/>
     </row>
-    <row r="59" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:19" customHeight="1" ht="18">
       <c r="A59" s="6"/>
       <c r="B59" s="6"/>
       <c r="C59" s="6"/>
@@ -1993,7 +2018,7 @@
       <c r="R59" s="6"/>
       <c r="S59" s="6"/>
     </row>
-    <row r="60" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:19" customHeight="1" ht="18">
       <c r="A60" s="7"/>
       <c r="B60" s="7"/>
       <c r="C60" s="7"/>
@@ -2014,7 +2039,7 @@
       <c r="R60" s="7"/>
       <c r="S60" s="7"/>
     </row>
-    <row r="61" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:19" customHeight="1" ht="18">
       <c r="A61" s="6"/>
       <c r="B61" s="6"/>
       <c r="C61" s="6"/>
@@ -2035,7 +2060,7 @@
       <c r="R61" s="6"/>
       <c r="S61" s="6"/>
     </row>
-    <row r="62" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:19" customHeight="1" ht="18">
       <c r="A62" s="7"/>
       <c r="B62" s="7"/>
       <c r="C62" s="7"/>
@@ -2056,7 +2081,7 @@
       <c r="R62" s="7"/>
       <c r="S62" s="7"/>
     </row>
-    <row r="63" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:19" customHeight="1" ht="18">
       <c r="A63" s="6"/>
       <c r="B63" s="6"/>
       <c r="C63" s="6"/>
@@ -2077,7 +2102,7 @@
       <c r="R63" s="6"/>
       <c r="S63" s="6"/>
     </row>
-    <row r="64" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:19" customHeight="1" ht="18">
       <c r="A64" s="7"/>
       <c r="B64" s="7"/>
       <c r="C64" s="7"/>
@@ -2098,7 +2123,7 @@
       <c r="R64" s="7"/>
       <c r="S64" s="7"/>
     </row>
-    <row r="65" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:19" customHeight="1" ht="18">
       <c r="A65" s="6"/>
       <c r="B65" s="6"/>
       <c r="C65" s="6"/>
@@ -2119,7 +2144,7 @@
       <c r="R65" s="6"/>
       <c r="S65" s="6"/>
     </row>
-    <row r="66" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:19" customHeight="1" ht="18">
       <c r="A66" s="7"/>
       <c r="B66" s="7"/>
       <c r="C66" s="7"/>
@@ -2140,7 +2165,7 @@
       <c r="R66" s="7"/>
       <c r="S66" s="7"/>
     </row>
-    <row r="67" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:19" customHeight="1" ht="18">
       <c r="A67" s="6"/>
       <c r="B67" s="6"/>
       <c r="C67" s="6"/>
@@ -2161,7 +2186,7 @@
       <c r="R67" s="6"/>
       <c r="S67" s="6"/>
     </row>
-    <row r="68" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:19" customHeight="1" ht="18">
       <c r="A68" s="7"/>
       <c r="B68" s="7"/>
       <c r="C68" s="7"/>
@@ -2182,7 +2207,7 @@
       <c r="R68" s="7"/>
       <c r="S68" s="7"/>
     </row>
-    <row r="69" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:19" customHeight="1" ht="18">
       <c r="A69" s="6"/>
       <c r="B69" s="6"/>
       <c r="C69" s="6"/>
@@ -2203,7 +2228,7 @@
       <c r="R69" s="6"/>
       <c r="S69" s="6"/>
     </row>
-    <row r="70" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:19" customHeight="1" ht="18">
       <c r="A70" s="7"/>
       <c r="B70" s="7"/>
       <c r="C70" s="7"/>
@@ -2224,7 +2249,7 @@
       <c r="R70" s="7"/>
       <c r="S70" s="7"/>
     </row>
-    <row r="71" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:19" customHeight="1" ht="18">
       <c r="A71" s="6"/>
       <c r="B71" s="6"/>
       <c r="C71" s="6"/>
@@ -2245,7 +2270,7 @@
       <c r="R71" s="6"/>
       <c r="S71" s="6"/>
     </row>
-    <row r="72" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:19" customHeight="1" ht="18">
       <c r="A72" s="7"/>
       <c r="B72" s="7"/>
       <c r="C72" s="7"/>
@@ -2266,7 +2291,7 @@
       <c r="R72" s="7"/>
       <c r="S72" s="7"/>
     </row>
-    <row r="73" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:19" customHeight="1" ht="18">
       <c r="A73" s="6"/>
       <c r="B73" s="6"/>
       <c r="C73" s="6"/>
@@ -2287,7 +2312,7 @@
       <c r="R73" s="6"/>
       <c r="S73" s="6"/>
     </row>
-    <row r="74" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:19" customHeight="1" ht="18">
       <c r="A74" s="7"/>
       <c r="B74" s="7"/>
       <c r="C74" s="7"/>
@@ -2308,7 +2333,7 @@
       <c r="R74" s="7"/>
       <c r="S74" s="7"/>
     </row>
-    <row r="75" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:19" customHeight="1" ht="18">
       <c r="A75" s="6"/>
       <c r="B75" s="6"/>
       <c r="C75" s="6"/>
@@ -2329,7 +2354,7 @@
       <c r="R75" s="6"/>
       <c r="S75" s="6"/>
     </row>
-    <row r="76" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:19" customHeight="1" ht="18">
       <c r="A76" s="7"/>
       <c r="B76" s="7"/>
       <c r="C76" s="7"/>
@@ -2350,7 +2375,7 @@
       <c r="R76" s="7"/>
       <c r="S76" s="7"/>
     </row>
-    <row r="77" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:19" customHeight="1" ht="18">
       <c r="A77" s="6"/>
       <c r="B77" s="6"/>
       <c r="C77" s="6"/>
@@ -2371,7 +2396,7 @@
       <c r="R77" s="6"/>
       <c r="S77" s="6"/>
     </row>
-    <row r="78" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:19" customHeight="1" ht="18">
       <c r="A78" s="7"/>
       <c r="B78" s="7"/>
       <c r="C78" s="7"/>
@@ -2392,7 +2417,7 @@
       <c r="R78" s="7"/>
       <c r="S78" s="7"/>
     </row>
-    <row r="79" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:19" customHeight="1" ht="18">
       <c r="A79" s="6"/>
       <c r="B79" s="6"/>
       <c r="C79" s="6"/>
@@ -2413,7 +2438,7 @@
       <c r="R79" s="6"/>
       <c r="S79" s="6"/>
     </row>
-    <row r="80" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:19" customHeight="1" ht="18">
       <c r="A80" s="7"/>
       <c r="B80" s="7"/>
       <c r="C80" s="7"/>
@@ -2434,7 +2459,7 @@
       <c r="R80" s="7"/>
       <c r="S80" s="7"/>
     </row>
-    <row r="81" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:19" customHeight="1" ht="18">
       <c r="A81" s="6"/>
       <c r="B81" s="6"/>
       <c r="C81" s="6"/>
@@ -2455,7 +2480,7 @@
       <c r="R81" s="6"/>
       <c r="S81" s="6"/>
     </row>
-    <row r="82" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:19" customHeight="1" ht="18">
       <c r="A82" s="7"/>
       <c r="B82" s="7"/>
       <c r="C82" s="7"/>
@@ -2476,7 +2501,7 @@
       <c r="R82" s="7"/>
       <c r="S82" s="7"/>
     </row>
-    <row r="83" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:19" customHeight="1" ht="18">
       <c r="A83" s="6"/>
       <c r="B83" s="6"/>
       <c r="C83" s="6"/>
@@ -2497,7 +2522,7 @@
       <c r="R83" s="6"/>
       <c r="S83" s="6"/>
     </row>
-    <row r="84" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:19" customHeight="1" ht="18">
       <c r="A84" s="7"/>
       <c r="B84" s="7"/>
       <c r="C84" s="7"/>
@@ -2518,7 +2543,7 @@
       <c r="R84" s="7"/>
       <c r="S84" s="7"/>
     </row>
-    <row r="85" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:19" customHeight="1" ht="18">
       <c r="A85" s="6"/>
       <c r="B85" s="6"/>
       <c r="C85" s="6"/>
@@ -2539,7 +2564,7 @@
       <c r="R85" s="6"/>
       <c r="S85" s="6"/>
     </row>
-    <row r="86" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:19" customHeight="1" ht="18">
       <c r="A86" s="7"/>
       <c r="B86" s="7"/>
       <c r="C86" s="7"/>
@@ -2560,7 +2585,7 @@
       <c r="R86" s="7"/>
       <c r="S86" s="7"/>
     </row>
-    <row r="87" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:19" customHeight="1" ht="18">
       <c r="A87" s="6"/>
       <c r="B87" s="6"/>
       <c r="C87" s="6"/>
@@ -2581,7 +2606,7 @@
       <c r="R87" s="6"/>
       <c r="S87" s="6"/>
     </row>
-    <row r="88" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:19" customHeight="1" ht="18">
       <c r="A88" s="7"/>
       <c r="B88" s="7"/>
       <c r="C88" s="7"/>
@@ -2602,7 +2627,7 @@
       <c r="R88" s="7"/>
       <c r="S88" s="7"/>
     </row>
-    <row r="89" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:19" customHeight="1" ht="18">
       <c r="A89" s="6"/>
       <c r="B89" s="6"/>
       <c r="C89" s="6"/>
@@ -2623,7 +2648,7 @@
       <c r="R89" s="6"/>
       <c r="S89" s="6"/>
     </row>
-    <row r="90" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:19" customHeight="1" ht="18">
       <c r="A90" s="7"/>
       <c r="B90" s="7"/>
       <c r="C90" s="7"/>
@@ -2644,7 +2669,7 @@
       <c r="R90" s="7"/>
       <c r="S90" s="7"/>
     </row>
-    <row r="91" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:19" customHeight="1" ht="18">
       <c r="A91" s="6"/>
       <c r="B91" s="6"/>
       <c r="C91" s="6"/>
@@ -2665,7 +2690,7 @@
       <c r="R91" s="6"/>
       <c r="S91" s="6"/>
     </row>
-    <row r="92" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:19" customHeight="1" ht="18">
       <c r="A92" s="7"/>
       <c r="B92" s="7"/>
       <c r="C92" s="7"/>
@@ -2686,7 +2711,7 @@
       <c r="R92" s="7"/>
       <c r="S92" s="7"/>
     </row>
-    <row r="93" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:19" customHeight="1" ht="18">
       <c r="A93" s="6"/>
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
@@ -2707,7 +2732,7 @@
       <c r="R93" s="6"/>
       <c r="S93" s="6"/>
     </row>
-    <row r="94" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:19" customHeight="1" ht="18">
       <c r="A94" s="7"/>
       <c r="B94" s="7"/>
       <c r="C94" s="7"/>
@@ -2728,7 +2753,7 @@
       <c r="R94" s="7"/>
       <c r="S94" s="7"/>
     </row>
-    <row r="95" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:19" customHeight="1" ht="18">
       <c r="A95" s="6"/>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
@@ -2749,7 +2774,7 @@
       <c r="R95" s="6"/>
       <c r="S95" s="6"/>
     </row>
-    <row r="96" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:19" customHeight="1" ht="18">
       <c r="A96" s="7"/>
       <c r="B96" s="7"/>
       <c r="C96" s="7"/>
@@ -2770,7 +2795,7 @@
       <c r="R96" s="7"/>
       <c r="S96" s="7"/>
     </row>
-    <row r="97" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:19" customHeight="1" ht="18">
       <c r="A97" s="6"/>
       <c r="B97" s="6"/>
       <c r="C97" s="6"/>
@@ -2791,7 +2816,7 @@
       <c r="R97" s="6"/>
       <c r="S97" s="6"/>
     </row>
-    <row r="98" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:19" customHeight="1" ht="18">
       <c r="A98" s="7"/>
       <c r="B98" s="7"/>
       <c r="C98" s="7"/>
@@ -2812,7 +2837,7 @@
       <c r="R98" s="7"/>
       <c r="S98" s="7"/>
     </row>
-    <row r="99" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:19" customHeight="1" ht="18">
       <c r="A99" s="6"/>
       <c r="B99" s="6"/>
       <c r="C99" s="6"/>
@@ -2833,7 +2858,7 @@
       <c r="R99" s="6"/>
       <c r="S99" s="6"/>
     </row>
-    <row r="100" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:19" customHeight="1" ht="18">
       <c r="A100" s="7"/>
       <c r="B100" s="7"/>
       <c r="C100" s="7"/>
@@ -2856,52 +2881,66 @@
     </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid" error="Choose from the dropdown list." promptTitle="Question Type" prompt="Pick the question type." sqref="C3:C100" xr:uid="{00000000-0002-0000-0000-000000000000}">
-      <formula1>"Yes / No,Free Text,Subjective,Dropdown,Multi select,Image,Video,Date,Date &amp; Time,File Upload,Location,Audio,Multi Response"</formula1>
+    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid" error="Choose from the dropdown list." promptTitle="Question Type" prompt="Pick the question type." sqref="C3:C100">
+      <formula1>"Yes / No,Free Text,Subjective,Dropdown,Multi select,Image,Video,Date,Date &amp; Time,File Upload,Location,Audio,Multi Response,Barcode,QR Code,RFID"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid" error="Choose from the dropdown list." promptTitle="Answer Type" prompt="Required or Optional?" sqref="D3:D100" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid" error="Choose from the dropdown list." promptTitle="Answer Type" prompt="Required or Optional?" sqref="D3:D100">
       <formula1>"Required,Optional"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid" error="Choose from the dropdown list." promptTitle="Multiple Answers Allowed" prompt="Multi select ONLY: Yes = auditor can pick multiple options._x000a_No or blank = single selection._x000a_Leave blank for all other question types." sqref="G3:G100" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid" error="Choose from the dropdown list." promptTitle="Multiple Answers Allowed" prompt="Multi select ONLY: Yes = auditor can pick multiple options._x000a_No or blank = single selection._x000a_Leave blank for all other question types." sqref="G3:G100">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid" error="Choose from the dropdown list." promptTitle="Allow Multiple Images" prompt="Image ONLY: Yes = auditor can upload multiple images (+ button shown)._x000a_No or blank = single image upload._x000a_Leave blank for all other question types." sqref="H3:H100" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid" error="Choose from the dropdown list." promptTitle="Allow Multiple Images" prompt="Image ONLY: Yes = auditor can upload multiple images (+ button shown)._x000a_No or blank = single image upload._x000a_Leave blank for all other question types." sqref="H3:H100">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid" error="Choose from the dropdown list." promptTitle="Validation Rule" prompt="none | numericrange | digitlength | textlength | email | phone | regex" sqref="I3:I100" xr:uid="{00000000-0002-0000-0000-000004000000}">
+    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid" error="Choose from the dropdown list." promptTitle="Validation Rule" prompt="none | numericrange | digitlength | textlength | email | phone | regex" sqref="I3:I100">
       <formula1>"none,numericrange,digitlength,textlength,email,phone,regex"</formula1>
     </dataValidation>
   </dataValidations>
+  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
+  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
+    <oddHeader/>
+    <oddFooter/>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <tableParts count="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
   <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="100" customWidth="1"/>
+    <col min="1" max="1" width="28" customWidth="true" style="0"/>
+    <col min="2" max="2" width="100" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" customHeight="1" ht="30">
       <c r="A1" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" customHeight="1" ht="30">
       <c r="A2" s="9" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" customHeight="1" ht="30">
       <c r="A3" s="10" t="s">
         <v>1</v>
       </c>
@@ -2909,39 +2948,39 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" customHeight="1" ht="30">
       <c r="A4" s="9" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" customHeight="1" ht="30">
       <c r="A5" s="10" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" customHeight="1" ht="30">
       <c r="A6" s="9" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" customHeight="1" ht="30">
       <c r="A7" s="10" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" customHeight="1" ht="30">
       <c r="A8" s="9" t="s">
         <v>6</v>
       </c>
@@ -2949,7 +2988,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" customHeight="1" ht="30">
       <c r="A9" s="10" t="s">
         <v>7</v>
       </c>
@@ -2957,7 +2996,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" customHeight="1" ht="30">
       <c r="A10" s="9" t="s">
         <v>8</v>
       </c>
@@ -2965,7 +3004,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" customHeight="1" ht="30">
       <c r="A11" s="10" t="s">
         <v>9</v>
       </c>
@@ -2973,7 +3012,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" customHeight="1" ht="30">
       <c r="A12" s="9" t="s">
         <v>10</v>
       </c>
@@ -2981,7 +3020,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" customHeight="1" ht="30">
       <c r="A13" s="10" t="s">
         <v>11</v>
       </c>
@@ -2989,7 +3028,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" customHeight="1" ht="30">
       <c r="A14" s="9" t="s">
         <v>12</v>
       </c>
@@ -2997,7 +3036,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" customHeight="1" ht="30">
       <c r="A15" s="10" t="s">
         <v>13</v>
       </c>
@@ -3005,7 +3044,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" customHeight="1" ht="30">
       <c r="A16" s="9" t="s">
         <v>14</v>
       </c>
@@ -3013,7 +3052,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" customHeight="1" ht="30">
       <c r="A17" s="10" t="s">
         <v>15</v>
       </c>
@@ -3021,7 +3060,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" customHeight="1" ht="30">
       <c r="A18" s="9" t="s">
         <v>16</v>
       </c>
@@ -3029,7 +3068,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" customHeight="1" ht="30">
       <c r="A19" s="10" t="s">
         <v>17</v>
       </c>
@@ -3037,7 +3076,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" customHeight="1" ht="30">
       <c r="A20" s="9" t="s">
         <v>18</v>
       </c>
@@ -3046,6 +3085,17 @@
       </c>
     </row>
   </sheetData>
+  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
+  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
+    <oddHeader/>
+    <oddFooter/>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <tableParts count="0"/>
 </worksheet>
 </file>